--- a/docs/fem/files/xslope_reinforce_fem.xlsx
+++ b/docs/fem/files/xslope_reinforce_fem.xlsx
@@ -2595,7 +2595,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M3" s="3">
         <v>0.0</v>
@@ -2662,7 +2662,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M4" s="3">
         <v>0.0</v>
@@ -2723,7 +2723,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M5" s="3">
         <v>0.0</v>
@@ -2784,7 +2784,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M6" s="3">
         <v>0.0</v>
@@ -2842,7 +2842,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="3">
         <v>0.0</v>
@@ -2900,7 +2900,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M8" s="3">
         <v>0.0</v>

--- a/docs/fem/files/xslope_reinforce_fem.xlsx
+++ b/docs/fem/files/xslope_reinforce_fem.xlsx
@@ -2595,7 +2595,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M3" s="3">
         <v>0.0</v>
@@ -2662,7 +2662,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M4" s="3">
         <v>0.0</v>
@@ -2723,7 +2723,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M5" s="3">
         <v>0.0</v>
@@ -2784,7 +2784,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M6" s="3">
         <v>0.0</v>
@@ -2842,7 +2842,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M7" s="3">
         <v>0.0</v>
@@ -2900,7 +2900,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M8" s="3">
         <v>0.0</v>

--- a/docs/fem/files/xslope_reinforce_fem.xlsx
+++ b/docs/fem/files/xslope_reinforce_fem.xlsx
@@ -6055,7 +6055,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>1000000.0</v>
       </c>
@@ -6179,7 +6181,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>1000000.0</v>
       </c>
